--- a/sample/evidence/A-04-training-register-fy2025.xlsx
+++ b/sample/evidence/A-04-training-register-fy2025.xlsx
@@ -527,7 +527,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>All departments, FY2025</t>
+          <t>Average hours of training per employee for the reporting period (FY2025)</t>
         </is>
       </c>
       <c r="B7" t="n">
